--- a/SEPE_Python_Avanzado_PUE/Tema 2 - PCAP/Examen/estudios/CopilotAnswers-20240528-225159.xlsx
+++ b/SEPE_Python_Avanzado_PUE/Tema 2 - PCAP/Examen/estudios/CopilotAnswers-20240528-225159.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27720"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EFB4ED91-93C1-4DDA-BA77-77A0BC8AA387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ismae\git\EstudiosPython\SEPE_Python_Avanzado_PUE\Tema 2 - PCAP\Examen\estudios\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB1CAA7C-A76D-40B5-99E8-F30265EE2EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -82,7 +85,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -99,7 +102,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -107,12 +110,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -453,60 +474,65 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="23.59765625" customWidth="1"/>
+    <col min="2" max="2" width="49.3984375" customWidth="1"/>
+    <col min="3" max="3" width="53.296875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:3" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
+    <row r="3" spans="1:3" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
+    <row r="4" spans="1:3" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
+    <row r="5" spans="1:3" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
